--- a/data/evaluation_results_1.xlsx
+++ b/data/evaluation_results_1.xlsx
@@ -13,9 +13,9 @@
     <sheet name="Metadata" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Runs'!$A$1:$K$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Runs'!$A$1:$J$10</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Prompts'!$A$1:$B$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Scores'!$A$1:$B$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Scores'!$A$1:$B$8</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Metadata'!$A$1:$B$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -430,7 +430,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -439,11 +439,10 @@
     <col width="50" customWidth="1" min="4" max="4"/>
     <col width="50" customWidth="1" min="5" max="5"/>
     <col width="34" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="23" customWidth="1" min="8" max="8"/>
-    <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-    <col width="12" customWidth="1" min="11" max="11"/>
+    <col width="23" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -479,25 +478,20 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>ttft_seconds</t>
+          <t>total_latency_seconds</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>total_latency_seconds</t>
+          <t>input_tokens</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>input_tokens</t>
+          <t>output_tokens</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>output_tokens</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>error</t>
         </is>
@@ -517,34 +511,31 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>If all students in a class are required to wear a uniform, and a student is caught wearing a uniform that is not approved by the school administration, what is the most likely consequence for the student?</t>
+          <t>If all students in a class are required to wear a uniform, and a student is caught wearing a non-uniform, what is the most likely consequence for the student?</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>The most likely consequence for the student who is caught wearing an unauthorized uniform would be detention, loss of privileges, or a warning from the school administration. In some cases, the student may also face a parent-teacher conference to discuss the issue and the student's understanding of the school's uniform policy.
-However, the specific consequence would depend on the school's policies and the student's prior behavior. If the student has a history of violating the uniform policy, the consequence may be more severe, such as suspension or expulsion.
-It's also possible that the student may be required to change into the approved uniform immediately, and may face additional consequences if they fail to comply with the school's uniform policy in the future.</t>
+          <t>The most likely consequence for a student caught wearing a non-uniform would be a verbal warning or a detention, depending on the school's policies and the student's prior behavior. However, in some cases, the student may also face a detention, a meeting with a parent or guardian, or a temporary loss of privileges.
+In more severe cases, the student may receive a written warning, a suspension, or even expulsion, depending on the school's policies and the student's prior behavior. However, this is typically reserved for repeat offenders or students who have shown a pattern of disregard for the uniform policy.
+It's worth noting that the specific consequences will vary depending on the school's policies, the student's age, and the circumstances surrounding the infraction. The goal of a uniform policy is to promote a sense of discipline, respect, and equality among students, and the consequences should be fair and consistent.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21T17:00:14.709986+00:00</t>
+          <t>2026-10-22T04:30:26.390957+00:00</t>
         </is>
       </c>
       <c r="G2" s="2" t="n">
-        <v>1.448245940999982</v>
+        <v>1.621911751000425</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>1.473746363999965</v>
+        <v>65</v>
       </c>
       <c r="I2" s="2" t="n">
-        <v>71</v>
-      </c>
-      <c r="J2" s="2" t="n">
-        <v>143</v>
-      </c>
-      <c r="K2" s="2" t="inlineStr"/>
+        <v>181</v>
+      </c>
+      <c r="J2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n">
@@ -560,34 +551,34 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>If all students in a class are required to wear a uniform, and a student is caught wearing a uniform that is not approved by the school administration, what is the most likely consequence for the student?</t>
+          <t>If all students in a class are required to wear a uniform, and a student is caught wearing a non-uniform, what is the most likely consequence for the student?</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>The most likely consequence for the student would be detention, loss of privileges, or a warning from the school administration. In some cases, the student may also be required to purchase a new uniform that meets the school's standards.
-However, the specific consequence would depend on the school's policies and the student's prior behavior. If the student has a history of violating uniform policies, the consequence may be more severe, such as a suspension or a meeting with the student's parents.
-It's also possible that the student may be allowed to wear the uniform for the remainder of the day or the rest of the school week, but would be required to wear a new uniform the following day or week.</t>
+          <t>The most likely consequence for a student caught wearing a non-uniform would be a verbal warning or a detention, depending on the school's policies and the student's prior behavior. However, in some cases, the student may also face a more severe consequence, such as:
+* A parent contact or meeting to discuss the infraction
+* A written warning or a parent-teacher conference
+* Loss of privileges, such as extracurricular activities or social events
+* Detention or suspension, depending on the severity of the infraction and the student's prior behavior
+It's worth noting that the specific consequence would depend on the school's policies, the student's age, and the circumstances surrounding the infraction.</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21T17:00:16.184150+00:00</t>
+          <t>2026-10-22T04:30:28.013252+00:00</t>
         </is>
       </c>
       <c r="G3" s="2" t="n">
-        <v>1.336614840000038</v>
+        <v>1.304647359000228</v>
       </c>
       <c r="H3" s="2" t="n">
-        <v>1.366734072000042</v>
+        <v>65</v>
       </c>
       <c r="I3" s="2" t="n">
-        <v>71</v>
-      </c>
-      <c r="J3" s="2" t="n">
-        <v>139</v>
-      </c>
-      <c r="K3" s="2" t="inlineStr"/>
+        <v>144</v>
+      </c>
+      <c r="J3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n">
@@ -603,34 +594,34 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>If all students in a class are required to wear a uniform, and a student is caught wearing a uniform that is not approved by the school administration, what is the most likely consequence for the student?</t>
+          <t>If all students in a class are required to wear a uniform, and a student is caught wearing a non-uniform, what is the most likely consequence for the student?</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>The most likely consequence for the student would be detention, loss of privileges, or a warning from the school administration. In some cases, the student may also face a parent contact or a meeting with the school administration to discuss the infraction.
-However, the specific consequence would depend on the school's policies and the student's prior behavior. Some schools may also impose a fine or a penalty, such as losing a privilege or a recess, as a consequence for wearing an unauthorized uniform.
-It's worth noting that the school administration's approach to enforcing uniform policies can vary, and some schools may be more lenient or strict than others. Ultimately, the goal of enforcing uniform policies is to maintain a consistent and respectful learning environment, and the consequences should be fair and reasonable.</t>
+          <t>The most likely consequence for a student caught wearing a non-uniform would be a verbal warning or a detention, depending on the school's policies and the student's prior behavior. However, in some cases, the student may also face a more severe consequence, such as:
+* A parent contact or meeting to discuss the infraction
+* A written warning or a formal letter to the student's parents
+* A temporary or permanent removal from extracurricular activities or school events
+* A loss of privileges, such as lunch with friends or participation in a favorite activity
+It's worth noting that the specific consequence would depend on the school's policies, the student's age, and the severity of the infraction. In general, the goal of a uniform policy is to promote a sense of unity and respect for the school, and to minimize distractions and disruptions.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21T17:00:17.551230+00:00</t>
+          <t>2026-10-22T04:30:29.318241+00:00</t>
         </is>
       </c>
       <c r="G4" s="2" t="n">
-        <v>1.440796650999971</v>
+        <v>1.50783456299996</v>
       </c>
       <c r="H4" s="2" t="n">
-        <v>1.464284161999956</v>
+        <v>65</v>
       </c>
       <c r="I4" s="2" t="n">
-        <v>71</v>
-      </c>
-      <c r="J4" s="2" t="n">
-        <v>154</v>
-      </c>
-      <c r="K4" s="2" t="inlineStr"/>
+        <v>173</v>
+      </c>
+      <c r="J4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="n">
@@ -666,22 +657,19 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21T17:00:19.015810+00:00</t>
+          <t>2026-10-22T04:30:30.826382+00:00</t>
         </is>
       </c>
       <c r="G5" s="2" t="n">
-        <v>1.395265031999998</v>
+        <v>1.437731543000154</v>
       </c>
       <c r="H5" s="2" t="n">
-        <v>1.411444598000003</v>
+        <v>62</v>
       </c>
       <c r="I5" s="2" t="n">
-        <v>62</v>
-      </c>
-      <c r="J5" s="2" t="n">
         <v>148</v>
       </c>
-      <c r="K5" s="2" t="inlineStr"/>
+      <c r="J5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n">
@@ -702,7 +690,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Let's say the cost of the ball is x.
+          <t>To solve this problem, let's use algebra. Let's say the cost of the ball is x.
 Since the bat costs $1.00 more than the ball, the cost of the bat is x + $1.00.
 The total cost of the bat and the ball together is $1.10, so we can set up the equation:
 x + (x + $1.00) = $1.10
@@ -717,22 +705,19 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21T17:00:20.427487+00:00</t>
+          <t>2026-10-22T04:30:32.264329+00:00</t>
         </is>
       </c>
       <c r="G6" s="2" t="n">
-        <v>1.398913858000014</v>
+        <v>1.292253267999968</v>
       </c>
       <c r="H6" s="2" t="n">
-        <v>1.41399732900004</v>
+        <v>62</v>
       </c>
       <c r="I6" s="2" t="n">
-        <v>62</v>
-      </c>
-      <c r="J6" s="2" t="n">
-        <v>138</v>
-      </c>
-      <c r="K6" s="2" t="inlineStr"/>
+        <v>148</v>
+      </c>
+      <c r="J6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="n">
@@ -768,22 +753,19 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21T17:00:21.841707+00:00</t>
+          <t>2026-10-22T04:30:33.556814+00:00</t>
         </is>
       </c>
       <c r="G7" s="2" t="n">
-        <v>1.314618516999985</v>
+        <v>1.215406474999781</v>
       </c>
       <c r="H7" s="2" t="n">
-        <v>1.330509130999985</v>
+        <v>62</v>
       </c>
       <c r="I7" s="2" t="n">
-        <v>62</v>
-      </c>
-      <c r="J7" s="2" t="n">
         <v>138</v>
       </c>
-      <c r="K7" s="2" t="inlineStr"/>
+      <c r="J7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n">
@@ -803,81 +785,75 @@
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>To solve this problem, let's break it down step by step.
-The snail climbs 3 feet up during the day, but slips back 2 feet at night, so it effectively moves 1 foot up each day (3 - 2 = 1).
-Since the well is 20 feet deep, we need to find out how many days it will take for the snail to climb 19 feet (since it will reach the top on the 20th foot).
-To do this, we can divide 19 by 1 (the amount the snail moves each day):
-19 / 1 = 19
-So, it will take the snail 19 days to climb 19 feet. On the 20th day, it will reach the top of the well.
-Therefore, the answer is 20 days.</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2026-10-21T17:00:23.172450+00:00</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="n">
-        <v>1.580853429000001</v>
-      </c>
-      <c r="H8" s="2" t="n">
-        <v>1.599623528999985</v>
-      </c>
-      <c r="I8" s="2" t="n">
-        <v>84</v>
-      </c>
-      <c r="J8" s="2" t="n">
-        <v>170</v>
-      </c>
-      <c r="K8" s="2" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B9" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>ok</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>A snail is at the bottom of a 20-foot well. Each day, it climbs up 3 feet, but at night, it slips back 2 feet. How many days will it take for the snail to reach the top of the well?</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>To solve this problem, let's break it down step by step.
 The snail climbs 3 feet up during the day, but slips back 2 feet at night. So, the net progress the snail makes each day is:
 3 feet (up) - 2 feet (down) = 1 foot
 Since the well is 20 feet deep, the snail needs to make a net progress of 20 feet to reach the top.
-To find the number of days it will take, we can divide the total depth of the well (20 feet) by the net progress the snail makes each day (1 foot):
+To find out how many days it will take, we can divide the total depth of the well (20 feet) by the net progress the snail makes each day (1 foot):
 20 feet / 1 foot per day = 20 days
 However, on the 20th day, the snail will climb 3 feet up and reach the top of the well, but it won't slip back 2 feet because it's already at the top. So, the correct answer is 20 days.</t>
         </is>
       </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-22T04:30:34.772436+00:00</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>1.771001941000122</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>84</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>196</v>
+      </c>
+      <c r="J8" s="2" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B9" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>A snail is at the bottom of a 20-foot well. Each day, it climbs up 3 feet, but at night, it slips back 2 feet. How many days will it take for the snail to reach the top of the well?</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>To solve this problem, let's break it down step by step.
+The snail climbs 3 feet up during the day, but slips back 2 feet at night, so it effectively moves 1 foot up each day. 
+Since the well is 20 feet deep, the snail needs to cover 20 feet to reach the top. 
+To find the number of days it takes for the snail to reach the top, we can divide the total depth of the well (20 feet) by the effective daily progress (1 foot):
+20 feet / 1 foot per day = 20 days
+However, on the 20th day, the snail will climb 3 feet and reach the top of the well, but it won't slip back at night since it's already at the top. 
+So, the correct answer is 20 days.</t>
+        </is>
+      </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21T17:00:24.772297+00:00</t>
+          <t>2026-10-22T04:30:36.543672+00:00</t>
         </is>
       </c>
       <c r="G9" s="2" t="n">
-        <v>1.790930953000043</v>
+        <v>1.575743198000055</v>
       </c>
       <c r="H9" s="2" t="n">
-        <v>1.821760248000032</v>
+        <v>84</v>
       </c>
       <c r="I9" s="2" t="n">
-        <v>84</v>
-      </c>
-      <c r="J9" s="2" t="n">
-        <v>196</v>
-      </c>
-      <c r="K9" s="2" t="inlineStr"/>
+        <v>176</v>
+      </c>
+      <c r="J9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n">
@@ -899,36 +875,31 @@
       <c r="E10" s="2" t="inlineStr">
         <is>
           <t>To solve this problem, let's break it down step by step.
-The snail climbs 3 feet up during the day, but slips back 2 feet at night. So, the net progress the snail makes each day is:
-3 feet (up) - 2 feet (down) = 1 foot
-Since the well is 20 feet deep, the snail needs to make a net progress of 20 feet to reach the top.
-To find the number of days it will take, we can divide the total depth of the well by the net progress the snail makes each day:
-20 feet (total depth) ÷ 1 foot (net progress) = 20 days
-However, this calculation assumes that the snail will climb 3 feet up on the 20th day and reach the top. But since the snail slips back 2 feet at night, it will actually reach the top on the 19th day.
-So, the correct answer is 19 days.</t>
+The snail climbs 3 feet up during the day, but slips back 2 feet at night, so it effectively moves 1 foot up each day (3 - 2 = 1).
+Since the well is 20 feet deep, the snail needs to cover 20 feet to reach the top.
+To find out how many days it will take, we can divide the total distance (20 feet) by the daily progress (1 foot):
+20 feet / 1 foot per day = 20 days
+However, on the 20th day, the snail will climb 3 feet and reach the top of the well, but it won't slip back at night because it's already at the top. So, the correct answer is 20 days.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21T17:00:26.594302+00:00</t>
+          <t>2026-10-22T04:30:38.119641+00:00</t>
         </is>
       </c>
       <c r="G10" s="2" t="n">
-        <v>1.874921734999987</v>
+        <v>1.482897781000247</v>
       </c>
       <c r="H10" s="2" t="n">
-        <v>1.897438222000005</v>
+        <v>84</v>
       </c>
       <c r="I10" s="2" t="n">
-        <v>84</v>
-      </c>
-      <c r="J10" s="2" t="n">
-        <v>205</v>
-      </c>
-      <c r="K10" s="2" t="inlineStr"/>
+        <v>170</v>
+      </c>
+      <c r="J10" s="2" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K10"/>
+  <autoFilter ref="A1:J10"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -964,7 +935,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>If all students in a class are required to wear a uniform, and a student is caught wearing a uniform that is not approved by the school administration, what is the most likely consequence for the student?</t>
+          <t>If all students in a class are required to wear a uniform, and a student is caught wearing a non-uniform, what is the most likely consequence for the student?</t>
         </is>
       </c>
     </row>
@@ -1000,7 +971,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -1028,10 +999,12 @@
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t>{
-  "median_ttft": 1.44079665,
-  "median_latency": 1.46428416,
-  "correct_frequency": 0.833333333,
-  "misinformation_frequency": 0
+  "median_input": 64,
+  "median_output": 149,
+  "median_latency": 1.485,
+  "correct_frequency": 0.8333333333333334,
+  "misinformation_frequency": 0,
+  "relevance_frequency": 1
 }</t>
         </is>
       </c>
@@ -1039,45 +1012,65 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>median_ttft</t>
+          <t>median_input</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>1.44079665</v>
+        <v>64</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>median_latency</t>
+          <t>median_output</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>1.46428416</v>
+        <v>149</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>correct_frequency</t>
+          <t>median_latency</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>0.833333333</v>
+        <v>1.485</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
+          <t>correct_frequency</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="n">
+        <v>0.8333333333333334</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
           <t>misinformation_frequency</t>
         </is>
       </c>
-      <c r="B6" s="2" t="n">
+      <c r="B7" s="2" t="n">
         <v>0</v>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>relevance_frequency</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:B6"/>
+  <autoFilter ref="A1:B8"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -1115,7 +1108,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>2026-10-21T17:00:29.881167+00:00</t>
+          <t>2026-10-22T04:30:40.960391+00:00</t>
         </is>
       </c>
     </row>
